--- a/示例-征地项目统计表模板.xlsx
+++ b/示例-征地项目统计表模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13493\Desktop\caodi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0CAB8D7-FD25-4F5C-8D79-1776629C4C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEB81354-C3D8-4983-8140-77BE6207513A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="分户面积表" sheetId="1" r:id="rId1"/>
@@ -668,7 +668,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -774,58 +774,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -918,20 +873,26 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -942,13 +903,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -960,35 +930,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -996,17 +951,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -1470,148 +1416,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:74" ht="32.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="37"/>
-      <c r="AN1" s="37"/>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="37"/>
-      <c r="AU1" s="37"/>
-      <c r="AV1" s="37"/>
-      <c r="AW1" s="37"/>
-      <c r="AX1" s="37"/>
-      <c r="AY1" s="37"/>
-      <c r="AZ1" s="37"/>
-      <c r="BA1" s="37"/>
-      <c r="BB1" s="37"/>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="37"/>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="37"/>
-      <c r="BG1" s="37"/>
-      <c r="BH1" s="37"/>
-      <c r="BI1" s="37"/>
-      <c r="BJ1" s="37"/>
-      <c r="BK1" s="37"/>
-      <c r="BL1" s="37"/>
-      <c r="BM1" s="37"/>
-      <c r="BN1" s="37"/>
-      <c r="BO1" s="37"/>
-      <c r="BP1" s="37"/>
-      <c r="BQ1" s="37"/>
-      <c r="BR1" s="37"/>
-      <c r="BS1" s="37"/>
-      <c r="BT1" s="37"/>
-      <c r="BU1" s="37"/>
-      <c r="BV1" s="37"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53"/>
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
+      <c r="AZ1" s="53"/>
+      <c r="BA1" s="53"/>
+      <c r="BB1" s="53"/>
+      <c r="BC1" s="53"/>
+      <c r="BD1" s="53"/>
+      <c r="BE1" s="53"/>
+      <c r="BF1" s="53"/>
+      <c r="BG1" s="53"/>
+      <c r="BH1" s="53"/>
+      <c r="BI1" s="53"/>
+      <c r="BJ1" s="53"/>
+      <c r="BK1" s="53"/>
+      <c r="BL1" s="53"/>
+      <c r="BM1" s="53"/>
+      <c r="BN1" s="53"/>
+      <c r="BO1" s="53"/>
+      <c r="BP1" s="53"/>
+      <c r="BQ1" s="53"/>
+      <c r="BR1" s="53"/>
+      <c r="BS1" s="53"/>
+      <c r="BT1" s="53"/>
+      <c r="BU1" s="53"/>
+      <c r="BV1" s="53"/>
     </row>
     <row r="2" spans="1:74" ht="25.8" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
-      <c r="Y2" s="56"/>
-      <c r="Z2" s="56"/>
-      <c r="AA2" s="56"/>
-      <c r="AB2" s="56"/>
-      <c r="AC2" s="56"/>
-      <c r="AD2" s="56"/>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="56"/>
-      <c r="AH2" s="56"/>
-      <c r="AI2" s="56"/>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="56"/>
-      <c r="AP2" s="56"/>
-      <c r="AQ2" s="57" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="44"/>
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="44"/>
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="AR2" s="57"/>
-      <c r="AS2" s="57"/>
-      <c r="AT2" s="57"/>
-      <c r="AU2" s="57"/>
-      <c r="AV2" s="57"/>
-      <c r="AW2" s="57"/>
-      <c r="AX2" s="57"/>
-      <c r="AY2" s="57"/>
-      <c r="AZ2" s="57"/>
-      <c r="BA2" s="57"/>
-      <c r="BB2" s="57"/>
-      <c r="BC2" s="57"/>
-      <c r="BD2" s="57"/>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="57"/>
-      <c r="BG2" s="57"/>
-      <c r="BH2" s="57"/>
+      <c r="AR2" s="45"/>
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="45"/>
+      <c r="AX2" s="45"/>
+      <c r="AY2" s="45"/>
+      <c r="AZ2" s="45"/>
+      <c r="BA2" s="45"/>
+      <c r="BB2" s="45"/>
+      <c r="BC2" s="45"/>
+      <c r="BD2" s="45"/>
+      <c r="BE2" s="45"/>
+      <c r="BF2" s="45"/>
+      <c r="BG2" s="45"/>
+      <c r="BH2" s="45"/>
       <c r="BI2" s="28"/>
       <c r="BJ2" s="28"/>
       <c r="BK2" s="28"/>
@@ -1628,216 +1574,216 @@
       <c r="BV2" s="28"/>
     </row>
     <row r="3" spans="1:74" ht="25.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="39" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="47"/>
+      <c r="AD3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="40"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="40"/>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="40"/>
-      <c r="AN3" s="40"/>
-      <c r="AO3" s="40"/>
-      <c r="AP3" s="40"/>
-      <c r="AQ3" s="40"/>
-      <c r="AR3" s="40"/>
-      <c r="AS3" s="40"/>
-      <c r="AT3" s="40"/>
-      <c r="AU3" s="40"/>
-      <c r="AV3" s="40"/>
-      <c r="AW3" s="40"/>
-      <c r="AX3" s="40"/>
-      <c r="AY3" s="40"/>
-      <c r="AZ3" s="40"/>
-      <c r="BA3" s="40"/>
-      <c r="BB3" s="40"/>
-      <c r="BC3" s="40"/>
-      <c r="BD3" s="40"/>
-      <c r="BE3" s="40"/>
-      <c r="BF3" s="40"/>
-      <c r="BG3" s="40"/>
-      <c r="BH3" s="40"/>
-      <c r="BI3" s="40"/>
-      <c r="BJ3" s="40"/>
-      <c r="BK3" s="40"/>
-      <c r="BL3" s="40"/>
-      <c r="BM3" s="40"/>
-      <c r="BN3" s="40"/>
-      <c r="BO3" s="40"/>
-      <c r="BP3" s="40"/>
-      <c r="BQ3" s="41"/>
-      <c r="BR3" s="39" t="s">
+      <c r="AE3" s="42"/>
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="42"/>
+      <c r="AK3" s="42"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="42"/>
+      <c r="AN3" s="42"/>
+      <c r="AO3" s="42"/>
+      <c r="AP3" s="42"/>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="42"/>
+      <c r="AS3" s="42"/>
+      <c r="AT3" s="42"/>
+      <c r="AU3" s="42"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
+      <c r="BB3" s="42"/>
+      <c r="BC3" s="42"/>
+      <c r="BD3" s="42"/>
+      <c r="BE3" s="42"/>
+      <c r="BF3" s="42"/>
+      <c r="BG3" s="42"/>
+      <c r="BH3" s="42"/>
+      <c r="BI3" s="42"/>
+      <c r="BJ3" s="42"/>
+      <c r="BK3" s="42"/>
+      <c r="BL3" s="42"/>
+      <c r="BM3" s="42"/>
+      <c r="BN3" s="42"/>
+      <c r="BO3" s="42"/>
+      <c r="BP3" s="42"/>
+      <c r="BQ3" s="43"/>
+      <c r="BR3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="BS3" s="40"/>
-      <c r="BT3" s="40"/>
-      <c r="BU3" s="41"/>
-      <c r="BV3" s="53" t="s">
+      <c r="BS3" s="42"/>
+      <c r="BT3" s="42"/>
+      <c r="BU3" s="43"/>
+      <c r="BV3" s="35" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:74" ht="25.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="44" t="s">
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38" t="s">
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="45" t="s">
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="S4" s="46"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="38" t="s">
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="38"/>
-      <c r="X4" s="43" t="s">
+      <c r="W4" s="47"/>
+      <c r="X4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="43"/>
-      <c r="AA4" s="43" t="s">
+      <c r="Y4" s="54"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="43"/>
-      <c r="AD4" s="48" t="s">
+      <c r="AB4" s="54"/>
+      <c r="AC4" s="54"/>
+      <c r="AD4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="AE4" s="38" t="s">
+      <c r="AE4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38" t="s">
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38" t="s">
+      <c r="AK4" s="47"/>
+      <c r="AL4" s="47"/>
+      <c r="AM4" s="47"/>
+      <c r="AN4" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="39" t="s">
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AR4" s="40"/>
-      <c r="AS4" s="40"/>
-      <c r="AT4" s="40"/>
-      <c r="AU4" s="40"/>
-      <c r="AV4" s="40"/>
-      <c r="AW4" s="40"/>
-      <c r="AX4" s="40"/>
-      <c r="AY4" s="41"/>
-      <c r="AZ4" s="39" t="s">
+      <c r="AR4" s="42"/>
+      <c r="AS4" s="42"/>
+      <c r="AT4" s="42"/>
+      <c r="AU4" s="42"/>
+      <c r="AV4" s="42"/>
+      <c r="AW4" s="42"/>
+      <c r="AX4" s="42"/>
+      <c r="AY4" s="43"/>
+      <c r="AZ4" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="BA4" s="40"/>
-      <c r="BB4" s="40"/>
-      <c r="BC4" s="40"/>
-      <c r="BD4" s="40"/>
-      <c r="BE4" s="41"/>
-      <c r="BF4" s="39" t="s">
+      <c r="BA4" s="42"/>
+      <c r="BB4" s="42"/>
+      <c r="BC4" s="42"/>
+      <c r="BD4" s="42"/>
+      <c r="BE4" s="43"/>
+      <c r="BF4" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="BG4" s="40"/>
-      <c r="BH4" s="40"/>
-      <c r="BI4" s="40"/>
-      <c r="BJ4" s="40"/>
-      <c r="BK4" s="40"/>
-      <c r="BL4" s="41"/>
-      <c r="BM4" s="39" t="s">
+      <c r="BG4" s="42"/>
+      <c r="BH4" s="42"/>
+      <c r="BI4" s="42"/>
+      <c r="BJ4" s="42"/>
+      <c r="BK4" s="42"/>
+      <c r="BL4" s="43"/>
+      <c r="BM4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="BN4" s="40"/>
-      <c r="BO4" s="41"/>
-      <c r="BP4" s="39" t="s">
+      <c r="BN4" s="42"/>
+      <c r="BO4" s="43"/>
+      <c r="BP4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="BQ4" s="41"/>
-      <c r="BR4" s="48" t="s">
+      <c r="BQ4" s="43"/>
+      <c r="BR4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="BS4" s="39" t="s">
+      <c r="BS4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="BT4" s="40"/>
-      <c r="BU4" s="40"/>
-      <c r="BV4" s="54"/>
+      <c r="BT4" s="42"/>
+      <c r="BU4" s="42"/>
+      <c r="BV4" s="36"/>
     </row>
     <row r="5" spans="1:74" ht="156" x14ac:dyDescent="0.25">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44" t="s">
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -1849,7 +1795,7 @@
       <c r="I5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="K5" s="6" t="s">
@@ -1861,7 +1807,7 @@
       <c r="M5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="N5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="O5" s="6" t="s">
@@ -1873,7 +1819,7 @@
       <c r="Q5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="R5" s="44" t="s">
+      <c r="R5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="S5" s="6" t="s">
@@ -1885,13 +1831,13 @@
       <c r="U5" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="V5" s="44" t="s">
+      <c r="V5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="W5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="X5" s="44" t="s">
+      <c r="X5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="Y5" s="6" t="s">
@@ -1900,7 +1846,7 @@
       <c r="Z5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AA5" s="44" t="s">
+      <c r="AA5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AB5" s="6" t="s">
@@ -1909,8 +1855,8 @@
       <c r="AC5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AD5" s="49"/>
-      <c r="AE5" s="44" t="s">
+      <c r="AD5" s="39"/>
+      <c r="AE5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AF5" s="6" t="s">
@@ -1925,7 +1871,7 @@
       <c r="AI5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AJ5" s="44" t="s">
+      <c r="AJ5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AK5" s="6" t="s">
@@ -1937,7 +1883,7 @@
       <c r="AM5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AN5" s="44" t="s">
+      <c r="AN5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AO5" s="6" t="s">
@@ -1946,7 +1892,7 @@
       <c r="AP5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AQ5" s="44" t="s">
+      <c r="AQ5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AR5" s="6" t="s">
@@ -1973,7 +1919,7 @@
       <c r="AY5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AZ5" s="44" t="s">
+      <c r="AZ5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BA5" s="6" t="s">
@@ -1991,7 +1937,7 @@
       <c r="BE5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BF5" s="44" t="s">
+      <c r="BF5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BG5" s="6" t="s">
@@ -2012,7 +1958,7 @@
       <c r="BL5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BM5" s="44" t="s">
+      <c r="BM5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BN5" s="6" t="s">
@@ -2021,14 +1967,14 @@
       <c r="BO5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BP5" s="44" t="s">
+      <c r="BP5" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BQ5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BR5" s="49"/>
-      <c r="BS5" s="48" t="s">
+      <c r="BR5" s="39"/>
+      <c r="BS5" s="38" t="s">
         <v>8</v>
       </c>
       <c r="BT5" s="16" t="s">
@@ -2037,15 +1983,15 @@
       <c r="BU5" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="BV5" s="54"/>
+      <c r="BV5" s="36"/>
     </row>
     <row r="6" spans="1:74" ht="25.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
       <c r="G6" s="11" t="s">
         <v>66</v>
       </c>
@@ -2055,7 +2001,7 @@
       <c r="I6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="44"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="11" t="s">
         <v>69</v>
       </c>
@@ -2065,7 +2011,7 @@
       <c r="M6" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="N6" s="44"/>
+      <c r="N6" s="46"/>
       <c r="O6" s="11" t="s">
         <v>72</v>
       </c>
@@ -2075,7 +2021,7 @@
       <c r="Q6" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="R6" s="44"/>
+      <c r="R6" s="46"/>
       <c r="S6" s="11" t="s">
         <v>75</v>
       </c>
@@ -2085,26 +2031,26 @@
       <c r="U6" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="V6" s="44"/>
+      <c r="V6" s="46"/>
       <c r="W6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="X6" s="44"/>
+      <c r="X6" s="46"/>
       <c r="Y6" s="11" t="s">
         <v>78</v>
       </c>
       <c r="Z6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AA6" s="44"/>
+      <c r="AA6" s="46"/>
       <c r="AB6" s="11" t="s">
         <v>80</v>
       </c>
       <c r="AC6" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AD6" s="50"/>
-      <c r="AE6" s="44"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="46"/>
       <c r="AF6" s="11" t="s">
         <v>82</v>
       </c>
@@ -2117,7 +2063,7 @@
       <c r="AI6" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="AJ6" s="44"/>
+      <c r="AJ6" s="46"/>
       <c r="AK6" s="11" t="s">
         <v>86</v>
       </c>
@@ -2127,14 +2073,14 @@
       <c r="AM6" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="AN6" s="44"/>
+      <c r="AN6" s="46"/>
       <c r="AO6" s="11" t="s">
         <v>89</v>
       </c>
       <c r="AP6" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="AQ6" s="44"/>
+      <c r="AQ6" s="46"/>
       <c r="AR6" s="11" t="s">
         <v>91</v>
       </c>
@@ -2159,7 +2105,7 @@
       <c r="AY6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="AZ6" s="44"/>
+      <c r="AZ6" s="46"/>
       <c r="BA6" s="11" t="s">
         <v>99</v>
       </c>
@@ -2175,7 +2121,7 @@
       <c r="BE6" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BF6" s="44"/>
+      <c r="BF6" s="46"/>
       <c r="BG6" s="11" t="s">
         <v>104</v>
       </c>
@@ -2194,26 +2140,26 @@
       <c r="BL6" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BM6" s="44"/>
+      <c r="BM6" s="46"/>
       <c r="BN6" s="11" t="s">
         <v>110</v>
       </c>
       <c r="BO6" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="BP6" s="44"/>
+      <c r="BP6" s="46"/>
       <c r="BQ6" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="BR6" s="50"/>
-      <c r="BS6" s="50"/>
+      <c r="BR6" s="40"/>
+      <c r="BS6" s="40"/>
       <c r="BT6" s="11" t="s">
         <v>114</v>
       </c>
       <c r="BU6" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="BV6" s="55"/>
+      <c r="BV6" s="37"/>
     </row>
     <row r="7" spans="1:74" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
@@ -35883,7 +35829,7 @@
       <c r="BU449" s="15"/>
       <c r="BV449" s="7"/>
     </row>
-    <row r="450" spans="1:74" s="13" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:74" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A450" s="7"/>
       <c r="B450" s="7"/>
       <c r="C450" s="14"/>
@@ -50779,84 +50725,114 @@
       <c r="BU645" s="33"/>
       <c r="BV645" s="7"/>
     </row>
-    <row r="646" spans="1:74" s="13" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A646" s="51"/>
-      <c r="B646" s="52"/>
-      <c r="C646" s="52"/>
-      <c r="D646" s="34"/>
-      <c r="E646" s="34"/>
-      <c r="F646" s="34"/>
-      <c r="G646" s="34"/>
-      <c r="H646" s="34"/>
-      <c r="I646" s="34"/>
-      <c r="J646" s="34"/>
-      <c r="K646" s="34"/>
-      <c r="L646" s="34"/>
-      <c r="M646" s="34"/>
-      <c r="N646" s="34"/>
-      <c r="O646" s="34"/>
-      <c r="P646" s="34"/>
-      <c r="Q646" s="34"/>
-      <c r="R646" s="34"/>
-      <c r="S646" s="34"/>
-      <c r="T646" s="34"/>
-      <c r="U646" s="34"/>
-      <c r="V646" s="34"/>
-      <c r="W646" s="34"/>
-      <c r="X646" s="34"/>
-      <c r="Y646" s="34"/>
-      <c r="Z646" s="34"/>
-      <c r="AA646" s="34"/>
-      <c r="AB646" s="34"/>
-      <c r="AC646" s="34"/>
-      <c r="AD646" s="34"/>
-      <c r="AE646" s="34"/>
-      <c r="AF646" s="34"/>
-      <c r="AG646" s="34"/>
-      <c r="AH646" s="34"/>
-      <c r="AI646" s="34"/>
-      <c r="AJ646" s="34"/>
-      <c r="AK646" s="34"/>
-      <c r="AL646" s="34"/>
-      <c r="AM646" s="34"/>
-      <c r="AN646" s="34"/>
-      <c r="AO646" s="34"/>
-      <c r="AP646" s="34"/>
-      <c r="AQ646" s="34"/>
-      <c r="AR646" s="34"/>
-      <c r="AS646" s="34"/>
-      <c r="AT646" s="34"/>
-      <c r="AU646" s="34"/>
-      <c r="AV646" s="34"/>
-      <c r="AW646" s="34"/>
-      <c r="AX646" s="34"/>
-      <c r="AY646" s="34"/>
-      <c r="AZ646" s="34"/>
-      <c r="BA646" s="34"/>
-      <c r="BB646" s="34"/>
-      <c r="BC646" s="34"/>
-      <c r="BD646" s="34"/>
-      <c r="BE646" s="34"/>
-      <c r="BF646" s="34"/>
-      <c r="BG646" s="34"/>
-      <c r="BH646" s="34"/>
-      <c r="BI646" s="34"/>
-      <c r="BJ646" s="34"/>
-      <c r="BK646" s="34"/>
-      <c r="BL646" s="34"/>
-      <c r="BM646" s="34"/>
-      <c r="BN646" s="34"/>
-      <c r="BO646" s="34"/>
-      <c r="BP646" s="34"/>
-      <c r="BQ646" s="34"/>
-      <c r="BR646" s="34"/>
-      <c r="BS646" s="34"/>
-      <c r="BT646" s="34"/>
-      <c r="BU646" s="36"/>
-      <c r="BV646" s="35"/>
+    <row r="646" spans="1:74" s="13" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A646" s="48"/>
+      <c r="B646" s="48"/>
+      <c r="C646" s="48"/>
+      <c r="D646" s="15"/>
+      <c r="E646" s="15"/>
+      <c r="F646" s="15"/>
+      <c r="G646" s="15"/>
+      <c r="H646" s="15"/>
+      <c r="I646" s="15"/>
+      <c r="J646" s="15"/>
+      <c r="K646" s="15"/>
+      <c r="L646" s="15"/>
+      <c r="M646" s="15"/>
+      <c r="N646" s="15"/>
+      <c r="O646" s="15"/>
+      <c r="P646" s="15"/>
+      <c r="Q646" s="15"/>
+      <c r="R646" s="15"/>
+      <c r="S646" s="15"/>
+      <c r="T646" s="15"/>
+      <c r="U646" s="15"/>
+      <c r="V646" s="15"/>
+      <c r="W646" s="15"/>
+      <c r="X646" s="15"/>
+      <c r="Y646" s="15"/>
+      <c r="Z646" s="15"/>
+      <c r="AA646" s="15"/>
+      <c r="AB646" s="15"/>
+      <c r="AC646" s="15"/>
+      <c r="AD646" s="15"/>
+      <c r="AE646" s="15"/>
+      <c r="AF646" s="15"/>
+      <c r="AG646" s="15"/>
+      <c r="AH646" s="15"/>
+      <c r="AI646" s="15"/>
+      <c r="AJ646" s="15"/>
+      <c r="AK646" s="15"/>
+      <c r="AL646" s="15"/>
+      <c r="AM646" s="15"/>
+      <c r="AN646" s="15"/>
+      <c r="AO646" s="15"/>
+      <c r="AP646" s="15"/>
+      <c r="AQ646" s="15"/>
+      <c r="AR646" s="15"/>
+      <c r="AS646" s="15"/>
+      <c r="AT646" s="15"/>
+      <c r="AU646" s="15"/>
+      <c r="AV646" s="15"/>
+      <c r="AW646" s="15"/>
+      <c r="AX646" s="15"/>
+      <c r="AY646" s="15"/>
+      <c r="AZ646" s="15"/>
+      <c r="BA646" s="15"/>
+      <c r="BB646" s="15"/>
+      <c r="BC646" s="15"/>
+      <c r="BD646" s="15"/>
+      <c r="BE646" s="15"/>
+      <c r="BF646" s="15"/>
+      <c r="BG646" s="15"/>
+      <c r="BH646" s="15"/>
+      <c r="BI646" s="15"/>
+      <c r="BJ646" s="15"/>
+      <c r="BK646" s="15"/>
+      <c r="BL646" s="15"/>
+      <c r="BM646" s="15"/>
+      <c r="BN646" s="15"/>
+      <c r="BO646" s="15"/>
+      <c r="BP646" s="15"/>
+      <c r="BQ646" s="15"/>
+      <c r="BR646" s="15"/>
+      <c r="BS646" s="15"/>
+      <c r="BT646" s="15"/>
+      <c r="BU646" s="15"/>
+      <c r="BV646" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="A1:BV1"/>
+    <mergeCell ref="E3:AC3"/>
+    <mergeCell ref="AD3:BQ3"/>
+    <mergeCell ref="B3:C6"/>
+    <mergeCell ref="AZ4:BE4"/>
+    <mergeCell ref="BF4:BL4"/>
+    <mergeCell ref="BM4:BO4"/>
+    <mergeCell ref="BP4:BQ4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AQ4:AY4"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="AE4:AI4"/>
+    <mergeCell ref="AJ4:AM4"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="R4:U4"/>
+    <mergeCell ref="AN4:AP4"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AD4:AD6"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="A646:C646"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F4:I4"/>
     <mergeCell ref="BV3:BV6"/>
     <mergeCell ref="BR4:BR6"/>
     <mergeCell ref="BS4:BU4"/>
@@ -50873,36 +50849,6 @@
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="J5:J6"/>
-    <mergeCell ref="A646:C646"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="AN4:AP4"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AD4:AD6"/>
-    <mergeCell ref="AE5:AE6"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="A1:BV1"/>
-    <mergeCell ref="E3:AC3"/>
-    <mergeCell ref="AD3:BQ3"/>
-    <mergeCell ref="B3:C6"/>
-    <mergeCell ref="AZ4:BE4"/>
-    <mergeCell ref="BF4:BL4"/>
-    <mergeCell ref="BM4:BO4"/>
-    <mergeCell ref="BP4:BQ4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AQ4:AY4"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AQ5:AQ6"/>
-    <mergeCell ref="AE4:AI4"/>
-    <mergeCell ref="AJ4:AM4"/>
-    <mergeCell ref="N5:N6"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -51147,332 +51093,332 @@
       </c>
     </row>
     <row r="3" spans="1:80" ht="25.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="60" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="60"/>
-      <c r="F3" s="39" t="s">
+      <c r="E3" s="55"/>
+      <c r="F3" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="40"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="40"/>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="40"/>
-      <c r="AN3" s="40"/>
-      <c r="AO3" s="40"/>
-      <c r="AP3" s="40"/>
-      <c r="AQ3" s="40"/>
-      <c r="AR3" s="40"/>
-      <c r="AS3" s="40"/>
-      <c r="AT3" s="40"/>
-      <c r="AU3" s="40"/>
-      <c r="AV3" s="40"/>
-      <c r="AW3" s="40"/>
-      <c r="AX3" s="40"/>
-      <c r="AY3" s="40"/>
-      <c r="AZ3" s="40"/>
-      <c r="BA3" s="40"/>
-      <c r="BB3" s="40"/>
-      <c r="BC3" s="40"/>
-      <c r="BD3" s="40"/>
-      <c r="BE3" s="40"/>
-      <c r="BF3" s="40"/>
-      <c r="BG3" s="40"/>
-      <c r="BH3" s="40"/>
-      <c r="BI3" s="40"/>
-      <c r="BJ3" s="40"/>
-      <c r="BK3" s="40"/>
-      <c r="BL3" s="40"/>
-      <c r="BM3" s="40"/>
-      <c r="BN3" s="40"/>
-      <c r="BO3" s="40"/>
-      <c r="BP3" s="40"/>
-      <c r="BQ3" s="40"/>
-      <c r="BR3" s="40"/>
-      <c r="BS3" s="40"/>
-      <c r="BT3" s="40"/>
-      <c r="BU3" s="40"/>
-      <c r="BV3" s="40"/>
-      <c r="BW3" s="41"/>
-      <c r="BX3" s="60" t="s">
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="42"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="42"/>
+      <c r="AE3" s="42"/>
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="42"/>
+      <c r="AK3" s="42"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="42"/>
+      <c r="AN3" s="42"/>
+      <c r="AO3" s="42"/>
+      <c r="AP3" s="42"/>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="42"/>
+      <c r="AS3" s="42"/>
+      <c r="AT3" s="42"/>
+      <c r="AU3" s="42"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
+      <c r="BB3" s="42"/>
+      <c r="BC3" s="42"/>
+      <c r="BD3" s="42"/>
+      <c r="BE3" s="42"/>
+      <c r="BF3" s="42"/>
+      <c r="BG3" s="42"/>
+      <c r="BH3" s="42"/>
+      <c r="BI3" s="42"/>
+      <c r="BJ3" s="42"/>
+      <c r="BK3" s="42"/>
+      <c r="BL3" s="42"/>
+      <c r="BM3" s="42"/>
+      <c r="BN3" s="42"/>
+      <c r="BO3" s="42"/>
+      <c r="BP3" s="42"/>
+      <c r="BQ3" s="42"/>
+      <c r="BR3" s="42"/>
+      <c r="BS3" s="42"/>
+      <c r="BT3" s="42"/>
+      <c r="BU3" s="42"/>
+      <c r="BV3" s="42"/>
+      <c r="BW3" s="43"/>
+      <c r="BX3" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="BY3" s="60" t="s">
+      <c r="BY3" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="BZ3" s="60" t="s">
+      <c r="BZ3" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="CA3" s="60" t="s">
+      <c r="CA3" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="CB3" s="38" t="s">
+      <c r="CB3" s="47" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:80" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="55" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="47"/>
+      <c r="X4" s="47"/>
+      <c r="Y4" s="47"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
+      <c r="AB4" s="47"/>
+      <c r="AC4" s="47"/>
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="47"/>
       <c r="AF4" s="19"/>
-      <c r="AG4" s="38" t="s">
+      <c r="AG4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
-      <c r="AK4" s="38"/>
-      <c r="AL4" s="38"/>
-      <c r="AM4" s="38"/>
-      <c r="AN4" s="38"/>
-      <c r="AO4" s="38"/>
-      <c r="AP4" s="38"/>
-      <c r="AQ4" s="38"/>
-      <c r="AR4" s="38"/>
-      <c r="AS4" s="38"/>
-      <c r="AT4" s="38"/>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="38"/>
-      <c r="AW4" s="38"/>
-      <c r="AX4" s="38"/>
-      <c r="AY4" s="38"/>
-      <c r="AZ4" s="38"/>
-      <c r="BA4" s="38"/>
-      <c r="BB4" s="38"/>
-      <c r="BC4" s="38"/>
-      <c r="BD4" s="38"/>
-      <c r="BE4" s="38"/>
-      <c r="BF4" s="38"/>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="38"/>
-      <c r="BI4" s="38"/>
-      <c r="BJ4" s="38"/>
-      <c r="BK4" s="38"/>
-      <c r="BL4" s="38"/>
-      <c r="BM4" s="38"/>
-      <c r="BN4" s="38"/>
-      <c r="BO4" s="38"/>
-      <c r="BP4" s="38"/>
-      <c r="BQ4" s="38"/>
-      <c r="BR4" s="38"/>
-      <c r="BS4" s="38"/>
-      <c r="BT4" s="38" t="s">
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="47"/>
+      <c r="AL4" s="47"/>
+      <c r="AM4" s="47"/>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="47"/>
+      <c r="AQ4" s="47"/>
+      <c r="AR4" s="47"/>
+      <c r="AS4" s="47"/>
+      <c r="AT4" s="47"/>
+      <c r="AU4" s="47"/>
+      <c r="AV4" s="47"/>
+      <c r="AW4" s="47"/>
+      <c r="AX4" s="47"/>
+      <c r="AY4" s="47"/>
+      <c r="AZ4" s="47"/>
+      <c r="BA4" s="47"/>
+      <c r="BB4" s="47"/>
+      <c r="BC4" s="47"/>
+      <c r="BD4" s="47"/>
+      <c r="BE4" s="47"/>
+      <c r="BF4" s="47"/>
+      <c r="BG4" s="47"/>
+      <c r="BH4" s="47"/>
+      <c r="BI4" s="47"/>
+      <c r="BJ4" s="47"/>
+      <c r="BK4" s="47"/>
+      <c r="BL4" s="47"/>
+      <c r="BM4" s="47"/>
+      <c r="BN4" s="47"/>
+      <c r="BO4" s="47"/>
+      <c r="BP4" s="47"/>
+      <c r="BQ4" s="47"/>
+      <c r="BR4" s="47"/>
+      <c r="BS4" s="47"/>
+      <c r="BT4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="BU4" s="38"/>
-      <c r="BV4" s="38"/>
-      <c r="BW4" s="38"/>
-      <c r="BX4" s="60"/>
-      <c r="BY4" s="60"/>
-      <c r="BZ4" s="60"/>
-      <c r="CA4" s="60"/>
-      <c r="CB4" s="38"/>
+      <c r="BU4" s="47"/>
+      <c r="BV4" s="47"/>
+      <c r="BW4" s="47"/>
+      <c r="BX4" s="55"/>
+      <c r="BY4" s="55"/>
+      <c r="BZ4" s="55"/>
+      <c r="CA4" s="55"/>
+      <c r="CB4" s="47"/>
     </row>
     <row r="5" spans="1:80" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="44" t="s">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38" t="s">
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38" t="s">
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="43" t="s">
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
       <c r="W5" s="27"/>
-      <c r="X5" s="38" t="s">
+      <c r="X5" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38" t="s">
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38" t="s">
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="44" t="s">
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="AG5" s="38" t="s">
+      <c r="AG5" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="38"/>
-      <c r="AL5" s="38" t="s">
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="AM5" s="38"/>
-      <c r="AN5" s="38"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="38" t="s">
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="AQ5" s="38"/>
-      <c r="AR5" s="38"/>
-      <c r="AS5" s="38" t="s">
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="47"/>
+      <c r="AS5" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="38"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="38"/>
-      <c r="AW5" s="38"/>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="38"/>
-      <c r="AZ5" s="38"/>
-      <c r="BA5" s="38"/>
-      <c r="BB5" s="38" t="s">
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="BC5" s="38"/>
-      <c r="BD5" s="38"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="38"/>
-      <c r="BG5" s="38"/>
-      <c r="BH5" s="38" t="s">
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
+      <c r="BG5" s="47"/>
+      <c r="BH5" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="BI5" s="38"/>
-      <c r="BJ5" s="38"/>
-      <c r="BK5" s="38"/>
-      <c r="BL5" s="38"/>
-      <c r="BM5" s="38"/>
-      <c r="BN5" s="38"/>
-      <c r="BO5" s="38" t="s">
+      <c r="BI5" s="47"/>
+      <c r="BJ5" s="47"/>
+      <c r="BK5" s="47"/>
+      <c r="BL5" s="47"/>
+      <c r="BM5" s="47"/>
+      <c r="BN5" s="47"/>
+      <c r="BO5" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="BP5" s="38"/>
-      <c r="BQ5" s="38"/>
-      <c r="BR5" s="38" t="s">
+      <c r="BP5" s="47"/>
+      <c r="BQ5" s="47"/>
+      <c r="BR5" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="BS5" s="38"/>
-      <c r="BT5" s="62" t="s">
+      <c r="BS5" s="47"/>
+      <c r="BT5" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="BU5" s="38" t="s">
+      <c r="BU5" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="BV5" s="38"/>
-      <c r="BW5" s="38"/>
-      <c r="BX5" s="60"/>
-      <c r="BY5" s="60"/>
-      <c r="BZ5" s="60"/>
-      <c r="CA5" s="60"/>
-      <c r="CB5" s="38"/>
+      <c r="BV5" s="47"/>
+      <c r="BW5" s="47"/>
+      <c r="BX5" s="55"/>
+      <c r="BY5" s="55"/>
+      <c r="BZ5" s="55"/>
+      <c r="CA5" s="55"/>
+      <c r="CB5" s="47"/>
     </row>
     <row r="6" spans="1:80" ht="156" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44" t="s">
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="I6" s="6" t="s">
@@ -51484,7 +51430,7 @@
       <c r="K6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="44" t="s">
+      <c r="L6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="M6" s="6" t="s">
@@ -51496,7 +51442,7 @@
       <c r="O6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="44" t="s">
+      <c r="P6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="Q6" s="6" t="s">
@@ -51508,7 +51454,7 @@
       <c r="S6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="44" t="s">
+      <c r="T6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="U6" s="6" t="s">
@@ -51520,13 +51466,13 @@
       <c r="W6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="44" t="s">
+      <c r="X6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="Y6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="Z6" s="44" t="s">
+      <c r="Z6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AA6" s="6" t="s">
@@ -51535,7 +51481,7 @@
       <c r="AB6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AC6" s="44" t="s">
+      <c r="AC6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AD6" s="6" t="s">
@@ -51544,8 +51490,8 @@
       <c r="AE6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AF6" s="44"/>
-      <c r="AG6" s="44" t="s">
+      <c r="AF6" s="46"/>
+      <c r="AG6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AH6" s="6" t="s">
@@ -51560,7 +51506,7 @@
       <c r="AK6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AL6" s="44" t="s">
+      <c r="AL6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AM6" s="6" t="s">
@@ -51572,7 +51518,7 @@
       <c r="AO6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AP6" s="44" t="s">
+      <c r="AP6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AQ6" s="6" t="s">
@@ -51581,7 +51527,7 @@
       <c r="AR6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AS6" s="44" t="s">
+      <c r="AS6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="AT6" s="6" t="s">
@@ -51608,7 +51554,7 @@
       <c r="BA6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BB6" s="44" t="s">
+      <c r="BB6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BC6" s="6" t="s">
@@ -51626,7 +51572,7 @@
       <c r="BG6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BH6" s="44" t="s">
+      <c r="BH6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BI6" s="6" t="s">
@@ -51647,7 +51593,7 @@
       <c r="BN6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BO6" s="44" t="s">
+      <c r="BO6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BP6" s="6" t="s">
@@ -51656,14 +51602,14 @@
       <c r="BQ6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BR6" s="44" t="s">
+      <c r="BR6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BS6" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BT6" s="62"/>
-      <c r="BU6" s="44" t="s">
+      <c r="BT6" s="56"/>
+      <c r="BU6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="BV6" s="18" t="s">
@@ -51672,21 +51618,21 @@
       <c r="BW6" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="BX6" s="60"/>
-      <c r="BY6" s="60"/>
-      <c r="BZ6" s="60"/>
-      <c r="CA6" s="60"/>
-      <c r="CB6" s="38"/>
+      <c r="BX6" s="55"/>
+      <c r="BY6" s="55"/>
+      <c r="BZ6" s="55"/>
+      <c r="CA6" s="55"/>
+      <c r="CB6" s="47"/>
     </row>
     <row r="7" spans="1:80" ht="25.8" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
       <c r="I7" s="11" t="s">
         <v>66</v>
       </c>
@@ -51696,7 +51642,7 @@
       <c r="K7" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="44"/>
+      <c r="L7" s="46"/>
       <c r="M7" s="11" t="s">
         <v>69</v>
       </c>
@@ -51706,7 +51652,7 @@
       <c r="O7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="P7" s="44"/>
+      <c r="P7" s="46"/>
       <c r="Q7" s="11" t="s">
         <v>72</v>
       </c>
@@ -51716,7 +51662,7 @@
       <c r="S7" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="T7" s="44"/>
+      <c r="T7" s="46"/>
       <c r="U7" s="11" t="s">
         <v>75</v>
       </c>
@@ -51726,26 +51672,26 @@
       <c r="W7" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="X7" s="44"/>
+      <c r="X7" s="46"/>
       <c r="Y7" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="Z7" s="44"/>
+      <c r="Z7" s="46"/>
       <c r="AA7" s="11" t="s">
         <v>78</v>
       </c>
       <c r="AB7" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AC7" s="44"/>
+      <c r="AC7" s="46"/>
       <c r="AD7" s="11" t="s">
         <v>80</v>
       </c>
       <c r="AE7" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AF7" s="44"/>
-      <c r="AG7" s="44"/>
+      <c r="AF7" s="46"/>
+      <c r="AG7" s="46"/>
       <c r="AH7" s="11" t="s">
         <v>82</v>
       </c>
@@ -51758,7 +51704,7 @@
       <c r="AK7" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="AL7" s="44"/>
+      <c r="AL7" s="46"/>
       <c r="AM7" s="11" t="s">
         <v>86</v>
       </c>
@@ -51768,14 +51714,14 @@
       <c r="AO7" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="AP7" s="44"/>
+      <c r="AP7" s="46"/>
       <c r="AQ7" s="11" t="s">
         <v>89</v>
       </c>
       <c r="AR7" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="AS7" s="44"/>
+      <c r="AS7" s="46"/>
       <c r="AT7" s="11" t="s">
         <v>91</v>
       </c>
@@ -51800,7 +51746,7 @@
       <c r="BA7" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="BB7" s="44"/>
+      <c r="BB7" s="46"/>
       <c r="BC7" s="11" t="s">
         <v>99</v>
       </c>
@@ -51816,7 +51762,7 @@
       <c r="BG7" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="BH7" s="44"/>
+      <c r="BH7" s="46"/>
       <c r="BI7" s="11" t="s">
         <v>104</v>
       </c>
@@ -51835,30 +51781,30 @@
       <c r="BN7" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="BO7" s="44"/>
+      <c r="BO7" s="46"/>
       <c r="BP7" s="11" t="s">
         <v>110</v>
       </c>
       <c r="BQ7" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="BR7" s="44"/>
+      <c r="BR7" s="46"/>
       <c r="BS7" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="BT7" s="63"/>
-      <c r="BU7" s="44"/>
+      <c r="BT7" s="57"/>
+      <c r="BU7" s="46"/>
       <c r="BV7" s="11" t="s">
         <v>136</v>
       </c>
       <c r="BW7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="BX7" s="60"/>
-      <c r="BY7" s="60"/>
-      <c r="BZ7" s="60"/>
-      <c r="CA7" s="60"/>
-      <c r="CB7" s="38"/>
+      <c r="BX7" s="55"/>
+      <c r="BY7" s="55"/>
+      <c r="BZ7" s="55"/>
+      <c r="CA7" s="55"/>
+      <c r="CB7" s="47"/>
     </row>
     <row r="8" spans="1:80" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
@@ -53009,11 +52955,11 @@
       <c r="CB21" s="19"/>
     </row>
     <row r="22" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
@@ -53110,6 +53056,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="G4:AE4"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="P5:S5"/>
+    <mergeCell ref="A1:CB1"/>
+    <mergeCell ref="A2:CA2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="BY3:BY7"/>
+    <mergeCell ref="BZ3:BZ7"/>
+    <mergeCell ref="CA3:CA7"/>
+    <mergeCell ref="CB3:CB7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="AF5:AF7"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="AL6:AL7"/>
+    <mergeCell ref="AP6:AP7"/>
+    <mergeCell ref="AS6:AS7"/>
+    <mergeCell ref="AG5:AK5"/>
+    <mergeCell ref="AL5:AO5"/>
+    <mergeCell ref="AP5:AR5"/>
+    <mergeCell ref="AS5:BA5"/>
     <mergeCell ref="BB6:BB7"/>
     <mergeCell ref="BH6:BH7"/>
     <mergeCell ref="BO6:BO7"/>
@@ -53126,45 +53111,6 @@
     <mergeCell ref="BT4:BW4"/>
     <mergeCell ref="F3:BW3"/>
     <mergeCell ref="AG6:AG7"/>
-    <mergeCell ref="AL6:AL7"/>
-    <mergeCell ref="AP6:AP7"/>
-    <mergeCell ref="AS6:AS7"/>
-    <mergeCell ref="AG5:AK5"/>
-    <mergeCell ref="AL5:AO5"/>
-    <mergeCell ref="AP5:AR5"/>
-    <mergeCell ref="AS5:BA5"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="A1:CB1"/>
-    <mergeCell ref="A2:CA2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="BY3:BY7"/>
-    <mergeCell ref="BZ3:BZ7"/>
-    <mergeCell ref="CA3:CA7"/>
-    <mergeCell ref="CB3:CB7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="X6:X7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="AF5:AF7"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="G4:AE4"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="T5:V5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="P5:S5"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -55966,105 +55912,105 @@
       <c r="B444" s="26"/>
       <c r="C444" s="26"/>
       <c r="D444" s="26"/>
-      <c r="E444" s="64"/>
+      <c r="E444" s="61"/>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="26"/>
       <c r="B445" s="26"/>
       <c r="C445" s="26"/>
       <c r="D445" s="26"/>
-      <c r="E445" s="64"/>
+      <c r="E445" s="61"/>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="26"/>
       <c r="B446" s="26"/>
       <c r="C446" s="26"/>
       <c r="D446" s="26"/>
-      <c r="E446" s="64"/>
+      <c r="E446" s="61"/>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="26"/>
       <c r="B447" s="26"/>
       <c r="C447" s="26"/>
       <c r="D447" s="26"/>
-      <c r="E447" s="64"/>
+      <c r="E447" s="61"/>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="26"/>
       <c r="B448" s="26"/>
       <c r="C448" s="26"/>
       <c r="D448" s="26"/>
-      <c r="E448" s="64"/>
+      <c r="E448" s="61"/>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="26"/>
       <c r="B449" s="26"/>
       <c r="C449" s="26"/>
       <c r="D449" s="26"/>
-      <c r="E449" s="64"/>
+      <c r="E449" s="61"/>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="26"/>
       <c r="B450" s="26"/>
       <c r="C450" s="26"/>
       <c r="D450" s="26"/>
-      <c r="E450" s="64"/>
+      <c r="E450" s="61"/>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="26"/>
       <c r="B451" s="26"/>
       <c r="C451" s="26"/>
       <c r="D451" s="26"/>
-      <c r="E451" s="64"/>
+      <c r="E451" s="61"/>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="26"/>
       <c r="B452" s="26"/>
       <c r="C452" s="26"/>
       <c r="D452" s="26"/>
-      <c r="E452" s="64"/>
+      <c r="E452" s="61"/>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="26"/>
       <c r="B453" s="26"/>
       <c r="C453" s="26"/>
       <c r="D453" s="26"/>
-      <c r="E453" s="64"/>
+      <c r="E453" s="61"/>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="26"/>
       <c r="B454" s="26"/>
       <c r="C454" s="26"/>
       <c r="D454" s="26"/>
-      <c r="E454" s="64"/>
+      <c r="E454" s="61"/>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="26"/>
       <c r="B455" s="26"/>
       <c r="C455" s="26"/>
       <c r="D455" s="26"/>
-      <c r="E455" s="64"/>
+      <c r="E455" s="61"/>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="26"/>
       <c r="B456" s="26"/>
       <c r="C456" s="26"/>
       <c r="D456" s="26"/>
-      <c r="E456" s="64"/>
+      <c r="E456" s="61"/>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="26"/>
       <c r="B457" s="26"/>
       <c r="C457" s="26"/>
       <c r="D457" s="26"/>
-      <c r="E457" s="64"/>
+      <c r="E457" s="61"/>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="26"/>
       <c r="B458" s="26"/>
       <c r="C458" s="26"/>
       <c r="D458" s="26"/>
-      <c r="E458" s="64"/>
+      <c r="E458" s="61"/>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="4"/>
